--- a/artfynd/A 49922-2021 artfynd.xlsx
+++ b/artfynd/A 49922-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49922-2021 artfynd.xlsx
+++ b/artfynd/A 49922-2021 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62817800</v>
+        <v>62817853</v>
       </c>
       <c r="B2" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599265.1256122697</v>
+        <v>599299</v>
       </c>
       <c r="R2" t="n">
-        <v>6819908.05209401</v>
+        <v>6819905</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2016-05-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-05-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,15 +759,15 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>äldre barrblandskog</t>
+          <t>olikåldrig gammal granskog i nordlut</t>
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # äldre asp</t>
+          <t>50 substratenheter # gamla granar</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -800,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62817799</v>
+        <v>62817800</v>
       </c>
       <c r="B3" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,21 +796,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -840,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599229.8459555744</v>
+        <v>599265</v>
       </c>
       <c r="R3" t="n">
-        <v>6820070.898629686</v>
+        <v>6819908</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,19 +853,9 @@
           <t>2016-05-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-05-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +869,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>asprik äldre blandskog</t>
+          <t>äldre barrblandskog</t>
         </is>
       </c>
       <c r="AN3" t="n">
@@ -925,15 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>62817853</v>
+        <v>62817799</v>
       </c>
       <c r="B4" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -965,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599299.17766432</v>
+        <v>599230</v>
       </c>
       <c r="R4" t="n">
-        <v>6819905.204830849</v>
+        <v>6820071</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,19 +963,9 @@
           <t>2016-05-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2016-05-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,15 +979,15 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>olikåldrig gammal granskog i nordlut</t>
+          <t>asprik äldre blandskog</t>
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>50 substratenheter # gamla granar</t>
+          <t>1 substratenheter # äldre asp</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
